--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T14:07:03+00:00</t>
+    <t>2026-04-09T12:24:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="181">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T12:24:05+00:00</t>
+    <t>2026-04-13T08:58:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -108,7 +108,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Base</t>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-entry</t>
   </si>
   <si>
     <t>Abstract</t>
@@ -250,10 +250,165 @@
     <t>Base</t>
   </si>
   <si>
+    <t>fr-lm-medication-prescription.header</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Base
+</t>
+  </si>
+  <si>
+    <t>Métadonnées de base</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.subject</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-patient-usager
+</t>
+  </si>
+  <si>
+    <t>Patient/subject information</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.subject</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.identifier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier
+</t>
+  </si>
+  <si>
+    <t>Identifiant de l’entrée</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.identifier</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.author[x]</t>
+  </si>
+  <si>
+    <t>author[x] peut correspondre soit à un professionnel, soit à une organisation, soit à un système.</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.performer</t>
+  </si>
+  <si>
+    <t>Exécutant (performer)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.performer</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.participant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
+</t>
+  </si>
+  <si>
+    <t>Participant</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.informant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+</t>
+  </si>
+  <si>
+    <t>Informateur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.informant</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dateTime
+</t>
+  </si>
+  <si>
+    <t>Date/Heure de création par l'auteur</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.date</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.source</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CodeableConcept
+</t>
+  </si>
+  <si>
+    <t>Source</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.source</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.langue</t>
+  </si>
+  <si>
+    <t>'fr-FR' pour français métropolitain (la casse des caractères doit être respectée)
+La partie en minuscules indique le code de la langue utilisée (ISO-639-1)
+La partie en majuscules indique le code pays (ISO-3166)</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.langue</t>
+  </si>
+  <si>
     <t>fr-lm-medication-prescription.status</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t xml:space="preserve">code
@@ -286,18 +441,10 @@
     <t>fr-lm-medication-prescription.intendedUseType</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept
-</t>
-  </si>
-  <si>
     <t>Objet de la prescription - prophylaxie, traitement, anesthésie, etc</t>
   </si>
   <si>
     <t>fr-lm-medication-prescription.periodOfUse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dateTime
-</t>
   </si>
   <si>
     <t>Durée du traitement</t>
@@ -334,10 +481,6 @@
   </si>
   <si>
     <t>fr-lm-medication-prescription.substitution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Base
-</t>
   </si>
   <si>
     <t>Autorisation de substitution</t>
@@ -736,11 +879,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ23"/>
+  <dimension ref="A1:AJ36"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="48.6484375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.6484375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="53.54296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="53.54296875" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -749,7 +892,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="74.25" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1071,7 +1214,7 @@
         <v>73</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="AG3" t="s" s="2">
         <v>79</v>
@@ -1088,10 +1231,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1114,13 +1257,13 @@
         <v>73</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1171,7 +1314,7 @@
         <v>73</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>82</v>
+        <v>86</v>
       </c>
       <c r="AG4" t="s" s="2">
         <v>79</v>
@@ -1188,10 +1331,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1214,13 +1357,13 @@
         <v>73</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1271,7 +1414,7 @@
         <v>73</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>74</v>
@@ -1288,10 +1431,10 @@
     </row>
     <row r="6">
       <c r="A6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1302,7 +1445,7 @@
         <v>74</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>73</v>
@@ -1314,13 +1457,13 @@
         <v>73</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="N6" s="2"/>
       <c r="O6" s="2"/>
@@ -1371,13 +1514,13 @@
         <v>73</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>88</v>
+        <v>93</v>
       </c>
       <c r="AG6" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>73</v>
@@ -1388,10 +1531,10 @@
     </row>
     <row r="7">
       <c r="A7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
@@ -1402,7 +1545,7 @@
         <v>74</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>73</v>
@@ -1414,13 +1557,13 @@
         <v>73</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
@@ -1471,13 +1614,13 @@
         <v>73</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="AG7" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>73</v>
@@ -1488,10 +1631,10 @@
     </row>
     <row r="8">
       <c r="A8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>94</v>
+        <v>98</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
@@ -1499,10 +1642,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>73</v>
@@ -1517,10 +1660,10 @@
         <v>95</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1571,13 +1714,13 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>73</v>
@@ -1588,10 +1731,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1602,7 +1745,7 @@
         <v>74</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>73</v>
@@ -1614,13 +1757,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>98</v>
+        <v>102</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>99</v>
+        <v>103</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1671,13 +1814,13 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>73</v>
@@ -1688,10 +1831,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>100</v>
+        <v>105</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1702,7 +1845,7 @@
         <v>74</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>73</v>
@@ -1714,13 +1857,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>101</v>
+        <v>95</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1771,13 +1914,13 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI10" t="s" s="2">
         <v>73</v>
@@ -1788,10 +1931,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1799,10 +1942,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>73</v>
@@ -1814,13 +1957,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -1871,13 +2014,13 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>73</v>
@@ -1888,10 +2031,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -1902,7 +2045,7 @@
         <v>74</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>73</v>
@@ -1914,13 +2057,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -1950,10 +2093,10 @@
         <v>73</v>
       </c>
       <c r="Y12" t="s" s="2">
-        <v>108</v>
+        <v>73</v>
       </c>
       <c r="Z12" t="s" s="2">
-        <v>109</v>
+        <v>73</v>
       </c>
       <c r="AA12" t="s" s="2">
         <v>73</v>
@@ -1971,13 +2114,13 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>106</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>73</v>
@@ -1988,10 +2131,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>110</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2014,13 +2157,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>86</v>
+        <v>117</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2071,7 +2214,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2088,10 +2231,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2114,13 +2257,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2171,7 +2314,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2188,10 +2331,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2214,13 +2357,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2271,7 +2414,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>115</v>
+        <v>126</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2288,10 +2431,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2314,13 +2457,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>104</v>
+        <v>128</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>119</v>
+        <v>129</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2371,7 +2514,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>118</v>
+        <v>127</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2388,10 +2531,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2414,13 +2557,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>121</v>
+        <v>131</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>122</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2471,7 +2614,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2488,10 +2631,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2514,13 +2657,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>86</v>
+        <v>134</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>124</v>
+        <v>135</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2571,7 +2714,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2588,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2614,13 +2757,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2671,7 +2814,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>125</v>
+        <v>136</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2688,10 +2831,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2699,7 +2842,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2714,13 +2857,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2771,10 +2914,10 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -2788,10 +2931,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2814,13 +2957,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>121</v>
+        <v>141</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -2871,7 +3014,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>130</v>
+        <v>140</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -2888,10 +3031,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -2899,7 +3042,7 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G22" t="s" s="2">
         <v>79</v>
@@ -2914,13 +3057,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -2971,10 +3114,10 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH22" t="s" s="2">
         <v>79</v>
@@ -2988,10 +3131,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -2999,7 +3142,7 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G23" t="s" s="2">
         <v>79</v>
@@ -3014,13 +3157,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3071,18 +3214,1318 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
+        <v>146</v>
+      </c>
+      <c r="AG23" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH23" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI23" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ23" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="B24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="C24" s="2"/>
+      <c r="D24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E24" s="2"/>
+      <c r="F24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K24" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="M24" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q24" s="2"/>
+      <c r="R24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF24" t="s" s="2">
+        <v>149</v>
+      </c>
+      <c r="AG24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH24" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI24" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ24" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="B25" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C25" s="2"/>
+      <c r="D25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E25" s="2"/>
+      <c r="F25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K25" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="L25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="M25" t="s" s="2">
+        <v>152</v>
+      </c>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q25" s="2"/>
+      <c r="R25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y25" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="Z25" t="s" s="2">
+        <v>154</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="AG25" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH25" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ25" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="B26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C26" s="2"/>
+      <c r="D26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E26" s="2"/>
+      <c r="F26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K26" t="s" s="2">
         <v>134</v>
       </c>
-      <c r="AG23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AH23" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI23" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AJ23" t="s" s="2">
+      <c r="L26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="M26" t="s" s="2">
+        <v>156</v>
+      </c>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q26" s="2"/>
+      <c r="R26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF26" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="AG26" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH26" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI26" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ26" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="B27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C27" s="2"/>
+      <c r="D27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2"/>
+      <c r="F27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K27" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="L27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="M27" t="s" s="2">
+        <v>159</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q27" s="2"/>
+      <c r="R27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF27" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="AG27" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH27" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI27" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ27" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B28" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="C28" s="2"/>
+      <c r="D28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E28" s="2"/>
+      <c r="F28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K28" t="s" s="2">
+        <v>161</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="M28" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q28" s="2"/>
+      <c r="R28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF28" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="AG28" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH28" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI28" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ28" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="B29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="C29" s="2"/>
+      <c r="D29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E29" s="2"/>
+      <c r="F29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K29" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="L29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="M29" t="s" s="2">
+        <v>164</v>
+      </c>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q29" s="2"/>
+      <c r="R29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF29" t="s" s="2">
+        <v>163</v>
+      </c>
+      <c r="AG29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH29" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI29" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ29" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="C30" s="2"/>
+      <c r="D30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E30" s="2"/>
+      <c r="F30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K30" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L30" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="M30" t="s" s="2">
+        <v>167</v>
+      </c>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q30" s="2"/>
+      <c r="R30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF30" t="s" s="2">
+        <v>165</v>
+      </c>
+      <c r="AG30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH30" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI30" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ30" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="B31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="C31" s="2"/>
+      <c r="D31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E31" s="2"/>
+      <c r="F31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="H31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K31" t="s" s="2">
+        <v>134</v>
+      </c>
+      <c r="L31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="M31" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N31" s="2"/>
+      <c r="O31" s="2"/>
+      <c r="P31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q31" s="2"/>
+      <c r="R31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF31" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="AG31" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH31" t="s" s="2">
+        <v>75</v>
+      </c>
+      <c r="AI31" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ31" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="B32" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="C32" s="2"/>
+      <c r="D32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E32" s="2"/>
+      <c r="F32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="G32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K32" t="s" s="2">
+        <v>171</v>
+      </c>
+      <c r="L32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="M32" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="N32" s="2"/>
+      <c r="O32" s="2"/>
+      <c r="P32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q32" s="2"/>
+      <c r="R32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF32" t="s" s="2">
+        <v>170</v>
+      </c>
+      <c r="AG32" t="s" s="2">
+        <v>74</v>
+      </c>
+      <c r="AH32" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI32" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ32" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="B33" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="C33" s="2"/>
+      <c r="D33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E33" s="2"/>
+      <c r="F33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K33" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L33" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="M33" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N33" s="2"/>
+      <c r="O33" s="2"/>
+      <c r="P33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q33" s="2"/>
+      <c r="R33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF33" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="AG33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH33" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI33" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ33" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="B34" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="C34" s="2"/>
+      <c r="D34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E34" s="2"/>
+      <c r="F34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K34" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L34" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="M34" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="N34" s="2"/>
+      <c r="O34" s="2"/>
+      <c r="P34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q34" s="2"/>
+      <c r="R34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF34" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH34" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI34" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ34" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="B35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="C35" s="2"/>
+      <c r="D35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E35" s="2"/>
+      <c r="F35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K35" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M35" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="N35" s="2"/>
+      <c r="O35" s="2"/>
+      <c r="P35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q35" s="2"/>
+      <c r="R35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF35" t="s" s="2">
+        <v>177</v>
+      </c>
+      <c r="AG35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH35" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI35" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ35" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="B36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="C36" s="2"/>
+      <c r="D36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E36" s="2"/>
+      <c r="F36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K36" t="s" s="2">
+        <v>166</v>
+      </c>
+      <c r="L36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="M36" t="s" s="2">
+        <v>180</v>
+      </c>
+      <c r="N36" s="2"/>
+      <c r="O36" s="2"/>
+      <c r="P36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q36" s="2"/>
+      <c r="R36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF36" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="AG36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH36" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI36" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ36" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T08:58:24+00:00</t>
+    <t>2026-04-13T09:04:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T09:04:52+00:00</t>
+    <t>2026-04-14T07:59:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="182">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-14T07:59:58+00:00</t>
+    <t>2026-04-16T07:11:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,39 +304,43 @@
     <t>fr-lm-medication-prescription.header.author[x].authorProfessional</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>L'auteur est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+</t>
+  </si>
+  <si>
+    <t>L'auteur est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.author[x].authorDevice</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.performer</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
 </t>
-  </si>
-  <si>
-    <t>L'auteur est un professionnel de santé</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorProfessional</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-prescription.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>L'auteur est une organisation</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorOrganisation</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-prescription.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
-</t>
-  </si>
-  <si>
-    <t>L'auteur est un système</t>
-  </si>
-  <si>
-    <t>fr-lm-entry.header.author[x].authorDevice</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-prescription.header.performer</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
@@ -892,7 +896,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="78.91015625" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1857,13 +1861,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>95</v>
+        <v>106</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1914,7 +1918,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1931,10 +1935,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1957,13 +1961,13 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
@@ -2014,7 +2018,7 @@
         <v>73</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>74</v>
@@ -2031,10 +2035,10 @@
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2057,13 +2061,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2114,7 +2118,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2131,10 +2135,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2157,13 +2161,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2214,7 +2218,7 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
@@ -2231,10 +2235,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2257,13 +2261,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2314,7 +2318,7 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
@@ -2331,10 +2335,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2357,13 +2361,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2414,7 +2418,7 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
@@ -2431,10 +2435,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2457,13 +2461,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2514,7 +2518,7 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>79</v>
@@ -2531,10 +2535,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2557,13 +2561,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2614,7 +2618,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2631,10 +2635,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2657,13 +2661,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2714,7 +2718,7 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
@@ -2731,10 +2735,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2757,13 +2761,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2814,7 +2818,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2831,10 +2835,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2857,13 +2861,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2914,7 +2918,7 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>74</v>
@@ -2931,10 +2935,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2957,13 +2961,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3014,7 +3018,7 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>79</v>
@@ -3031,10 +3035,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3057,13 +3061,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3114,7 +3118,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3131,10 +3135,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3157,13 +3161,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3214,7 +3218,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3231,10 +3235,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3260,10 +3264,10 @@
         <v>80</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3314,7 +3318,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3331,10 +3335,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3357,13 +3361,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3393,10 +3397,10 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="Z25" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="AA25" t="s" s="2">
         <v>73</v>
@@ -3414,7 +3418,7 @@
         <v>73</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3431,10 +3435,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3457,13 +3461,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3514,7 +3518,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3531,10 +3535,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3557,13 +3561,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3614,7 +3618,7 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>74</v>
@@ -3631,10 +3635,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3657,13 +3661,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3714,7 +3718,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3731,10 +3735,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3760,10 +3764,10 @@
         <v>80</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3814,7 +3818,7 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>79</v>
@@ -3831,10 +3835,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3857,13 +3861,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3914,7 +3918,7 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>79</v>
@@ -3931,10 +3935,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3957,13 +3961,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4014,7 +4018,7 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
@@ -4031,10 +4035,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4057,13 +4061,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4114,7 +4118,7 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>74</v>
@@ -4131,10 +4135,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4157,13 +4161,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4214,7 +4218,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4231,10 +4235,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4257,13 +4261,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4314,7 +4318,7 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>79</v>
@@ -4331,10 +4335,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4357,13 +4361,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4414,7 +4418,7 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>79</v>
@@ -4431,10 +4435,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4457,13 +4461,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4514,7 +4518,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1158" uniqueCount="182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1251" uniqueCount="193">
   <si>
     <t>Property</t>
   </si>
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0-snapsnot</t>
+    <t>0.1.0-snapshot</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-16T07:11:11+00:00</t>
+    <t>2026-04-24T08:31:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -304,7 +304,7 @@
     <t>fr-lm-medication-prescription.header.author[x].authorProfessional</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
 </t>
   </si>
   <si>
@@ -317,6 +317,10 @@
     <t>fr-lm-medication-prescription.header.author[x].authorOrganisation</t>
   </si>
   <si>
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation
+</t>
+  </si>
+  <si>
     <t>L'auteur est une organisation</t>
   </si>
   <si>
@@ -326,7 +330,7 @@
     <t>fr-lm-medication-prescription.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-systeme-structure-auteur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-device
 </t>
   </si>
   <si>
@@ -336,36 +340,59 @@
     <t>fr-lm-entry.header.author[x].authorDevice</t>
   </si>
   <si>
-    <t>fr-lm-medication-prescription.header.performer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-personne-structure
-</t>
+    <t>fr-lm-medication-prescription.header.performer[x]</t>
+  </si>
+  <si>
+    <t>https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-health-professional
+https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-organisation</t>
   </si>
   <si>
     <t>Exécutant (performer)</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.performer</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-prescription.header.participant</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-participant-corps
-</t>
+    <t>fr-lm-entry.header.performer[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.participant[x]</t>
   </si>
   <si>
     <t>Participant</t>
   </si>
   <si>
-    <t>fr-lm-entry.header.participant</t>
+    <t>fr-lm-entry.header.participant[x]</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>Le participant est un professionnel de santé</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantProfessional</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>Le participant est une organisation</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantOrganisation</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.participant[x].participantDevice</t>
+  </si>
+  <si>
+    <t>Le participant est un système</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.participant[x].participantDevice</t>
   </si>
   <si>
     <t>fr-lm-medication-prescription.header.informant</t>
   </si>
   <si>
-    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informateur
+    <t xml:space="preserve">https://interop.esante.gouv.fr/ig/document/core/StructureDefinition/fr-lm-informant
 </t>
   </si>
   <si>
@@ -388,11 +415,26 @@
     <t>fr-lm-entry.header.date</t>
   </si>
   <si>
-    <t>fr-lm-medication-prescription.header.source</t>
+    <t>fr-lm-medication-prescription.header.status</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
+  </si>
+  <si>
+    <t>Statut de l'acte</t>
+  </si>
+  <si>
+    <t>jdv-hl7-v3-ActStatus-cisis (2.16.840.1.113883.1.11.15933)</t>
+  </si>
+  <si>
+    <t>https://smt.esante.gouv.fr/fhir/ValueSet/jdv-hl7-v3-ActStatus-cisis</t>
+  </si>
+  <si>
+    <t>fr-lm-entry.header.status</t>
+  </si>
+  <si>
+    <t>fr-lm-medication-prescription.header.source</t>
   </si>
   <si>
     <t>Source</t>
@@ -410,16 +452,6 @@
   </si>
   <si>
     <t>fr-lm-entry.header.langue</t>
-  </si>
-  <si>
-    <t>fr-lm-medication-prescription.status</t>
-  </si>
-  <si>
-    <t xml:space="preserve">code
-</t>
-  </si>
-  <si>
-    <t>Statut de l'entrée</t>
   </si>
   <si>
     <t>fr-lm-medication-prescription.medication</t>
@@ -883,11 +915,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AJ36"/>
+  <dimension ref="A1:AJ39"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.54296875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="53.54296875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="60.25" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="60.25" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -896,7 +928,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="79.609375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="74.25" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -910,7 +942,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="27.48046875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="47.0546875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="74.33984375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1661,13 +1693,13 @@
         <v>73</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>95</v>
+        <v>99</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N8" s="2"/>
       <c r="O8" s="2"/>
@@ -1718,7 +1750,7 @@
         <v>73</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="AG8" t="s" s="2">
         <v>74</v>
@@ -1735,10 +1767,10 @@
     </row>
     <row r="9">
       <c r="A9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -1761,13 +1793,13 @@
         <v>73</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -1818,7 +1850,7 @@
         <v>73</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG9" t="s" s="2">
         <v>74</v>
@@ -1835,10 +1867,10 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C10" s="2"/>
       <c r="D10" t="s" s="2">
@@ -1861,13 +1893,13 @@
         <v>73</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -1918,7 +1950,7 @@
         <v>73</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="AG10" t="s" s="2">
         <v>74</v>
@@ -1935,10 +1967,10 @@
     </row>
     <row r="11">
       <c r="A11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
@@ -1961,7 +1993,7 @@
         <v>73</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="L11" t="s" s="2">
         <v>111</v>
@@ -2061,13 +2093,13 @@
         <v>73</v>
       </c>
       <c r="K12" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="L12" t="s" s="2">
         <v>114</v>
       </c>
-      <c r="L12" t="s" s="2">
-        <v>115</v>
-      </c>
       <c r="M12" t="s" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
@@ -2118,7 +2150,7 @@
         <v>73</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>74</v>
@@ -2135,10 +2167,10 @@
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2149,7 +2181,7 @@
         <v>74</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>73</v>
@@ -2161,13 +2193,13 @@
         <v>73</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>118</v>
+        <v>99</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" s="2"/>
@@ -2218,13 +2250,13 @@
         <v>73</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>73</v>
@@ -2235,10 +2267,10 @@
     </row>
     <row r="14">
       <c r="A14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2249,7 +2281,7 @@
         <v>74</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>73</v>
@@ -2261,13 +2293,13 @@
         <v>73</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>122</v>
+        <v>103</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -2318,13 +2350,13 @@
         <v>73</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>73</v>
@@ -2335,10 +2367,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2349,7 +2381,7 @@
         <v>74</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H15" t="s" s="2">
         <v>73</v>
@@ -2361,13 +2393,13 @@
         <v>73</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -2418,13 +2450,13 @@
         <v>73</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>73</v>
@@ -2435,10 +2467,10 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2446,7 +2478,7 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G16" t="s" s="2">
         <v>79</v>
@@ -2461,13 +2493,13 @@
         <v>73</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2518,10 +2550,10 @@
         <v>73</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH16" t="s" s="2">
         <v>79</v>
@@ -2535,10 +2567,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -2561,13 +2593,13 @@
         <v>73</v>
       </c>
       <c r="K17" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="L17" t="s" s="2">
         <v>132</v>
       </c>
-      <c r="L17" t="s" s="2">
-        <v>133</v>
-      </c>
       <c r="M17" t="s" s="2">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -2597,10 +2629,10 @@
         <v>73</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>73</v>
+        <v>133</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>73</v>
+        <v>134</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>73</v>
@@ -2618,7 +2650,7 @@
         <v>73</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>79</v>
@@ -2635,10 +2667,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -2649,7 +2681,7 @@
         <v>74</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H18" t="s" s="2">
         <v>73</v>
@@ -2661,13 +2693,13 @@
         <v>73</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -2718,13 +2750,13 @@
         <v>73</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>73</v>
@@ -2735,10 +2767,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -2761,13 +2793,13 @@
         <v>73</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -2818,7 +2850,7 @@
         <v>73</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>74</v>
@@ -2835,10 +2867,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -2846,7 +2878,7 @@
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G20" t="s" s="2">
         <v>79</v>
@@ -2861,13 +2893,13 @@
         <v>73</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
@@ -2918,10 +2950,10 @@
         <v>73</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH20" t="s" s="2">
         <v>79</v>
@@ -2935,10 +2967,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -2946,10 +2978,10 @@
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>73</v>
@@ -2961,13 +2993,13 @@
         <v>73</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
@@ -3018,13 +3050,13 @@
         <v>73</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>73</v>
@@ -3035,10 +3067,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3061,13 +3093,13 @@
         <v>73</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>145</v>
+        <v>131</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3118,7 +3150,7 @@
         <v>73</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>74</v>
@@ -3135,10 +3167,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3161,13 +3193,13 @@
         <v>73</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>148</v>
+        <v>127</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3218,7 +3250,7 @@
         <v>73</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>74</v>
@@ -3235,10 +3267,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3261,13 +3293,13 @@
         <v>73</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>80</v>
+        <v>153</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" s="2"/>
@@ -3318,7 +3350,7 @@
         <v>73</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>79</v>
@@ -3335,10 +3367,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -3361,13 +3393,13 @@
         <v>73</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>122</v>
+        <v>156</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" s="2"/>
@@ -3397,28 +3429,28 @@
         <v>73</v>
       </c>
       <c r="Y25" t="s" s="2">
-        <v>154</v>
+        <v>73</v>
       </c>
       <c r="Z25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE25" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF25" t="s" s="2">
         <v>155</v>
-      </c>
-      <c r="AA25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AB25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AC25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AD25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AE25" t="s" s="2">
-        <v>73</v>
-      </c>
-      <c r="AF25" t="s" s="2">
-        <v>152</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>74</v>
@@ -3435,10 +3467,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -3461,13 +3493,13 @@
         <v>73</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>135</v>
+        <v>159</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -3518,7 +3550,7 @@
         <v>73</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>74</v>
@@ -3535,10 +3567,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -3546,7 +3578,7 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G27" t="s" s="2">
         <v>79</v>
@@ -3561,13 +3593,13 @@
         <v>73</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>159</v>
+        <v>80</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -3618,10 +3650,10 @@
         <v>73</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH27" t="s" s="2">
         <v>79</v>
@@ -3635,10 +3667,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -3661,13 +3693,13 @@
         <v>73</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>162</v>
+        <v>131</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -3697,10 +3729,10 @@
         <v>73</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>73</v>
+        <v>165</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>73</v>
+        <v>166</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>73</v>
@@ -3718,7 +3750,7 @@
         <v>73</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>74</v>
@@ -3735,10 +3767,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -3746,7 +3778,7 @@
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G29" t="s" s="2">
         <v>79</v>
@@ -3761,13 +3793,13 @@
         <v>73</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>80</v>
+        <v>146</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" s="2"/>
@@ -3818,10 +3850,10 @@
         <v>73</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="AG29" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH29" t="s" s="2">
         <v>79</v>
@@ -3835,10 +3867,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -3846,7 +3878,7 @@
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G30" t="s" s="2">
         <v>79</v>
@@ -3861,13 +3893,13 @@
         <v>73</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -3918,10 +3950,10 @@
         <v>73</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="AG30" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH30" t="s" s="2">
         <v>79</v>
@@ -3935,10 +3967,10 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -3949,7 +3981,7 @@
         <v>74</v>
       </c>
       <c r="G31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="H31" t="s" s="2">
         <v>73</v>
@@ -3961,13 +3993,13 @@
         <v>73</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>135</v>
+        <v>173</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" s="2"/>
@@ -4018,13 +4050,13 @@
         <v>73</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>74</v>
       </c>
       <c r="AH31" t="s" s="2">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="AI31" t="s" s="2">
         <v>73</v>
@@ -4035,10 +4067,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4046,7 +4078,7 @@
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="G32" t="s" s="2">
         <v>79</v>
@@ -4061,13 +4093,13 @@
         <v>73</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>172</v>
+        <v>80</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" s="2"/>
@@ -4118,10 +4150,10 @@
         <v>73</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AG32" t="s" s="2">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AH32" t="s" s="2">
         <v>79</v>
@@ -4135,10 +4167,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -4161,13 +4193,13 @@
         <v>73</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -4218,7 +4250,7 @@
         <v>73</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>79</v>
@@ -4235,10 +4267,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -4246,10 +4278,10 @@
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H34" t="s" s="2">
         <v>73</v>
@@ -4261,13 +4293,13 @@
         <v>73</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>167</v>
+        <v>146</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -4318,13 +4350,13 @@
         <v>73</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="AG34" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH34" t="s" s="2">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="AI34" t="s" s="2">
         <v>73</v>
@@ -4335,10 +4367,10 @@
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -4346,7 +4378,7 @@
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="G35" t="s" s="2">
         <v>79</v>
@@ -4361,13 +4393,13 @@
         <v>73</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>179</v>
+        <v>184</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" s="2"/>
@@ -4418,10 +4450,10 @@
         <v>73</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
-        <v>79</v>
+        <v>74</v>
       </c>
       <c r="AH35" t="s" s="2">
         <v>79</v>
@@ -4435,10 +4467,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -4461,13 +4493,13 @@
         <v>73</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>181</v>
+        <v>186</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" s="2"/>
@@ -4518,7 +4550,7 @@
         <v>73</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>180</v>
+        <v>185</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>79</v>
@@ -4530,6 +4562,306 @@
         <v>73</v>
       </c>
       <c r="AJ36" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="B37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="C37" s="2"/>
+      <c r="D37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E37" s="2"/>
+      <c r="F37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K37" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="M37" t="s" s="2">
+        <v>188</v>
+      </c>
+      <c r="N37" s="2"/>
+      <c r="O37" s="2"/>
+      <c r="P37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q37" s="2"/>
+      <c r="R37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF37" t="s" s="2">
+        <v>187</v>
+      </c>
+      <c r="AG37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH37" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI37" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ37" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="B38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="C38" s="2"/>
+      <c r="D38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E38" s="2"/>
+      <c r="F38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K38" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="M38" t="s" s="2">
+        <v>190</v>
+      </c>
+      <c r="N38" s="2"/>
+      <c r="O38" s="2"/>
+      <c r="P38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q38" s="2"/>
+      <c r="R38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF38" t="s" s="2">
+        <v>189</v>
+      </c>
+      <c r="AG38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH38" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI38" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ38" t="s" s="2">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="B39" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="C39" s="2"/>
+      <c r="D39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="E39" s="2"/>
+      <c r="F39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="G39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="I39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="J39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="K39" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="L39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="M39" t="s" s="2">
+        <v>192</v>
+      </c>
+      <c r="N39" s="2"/>
+      <c r="O39" s="2"/>
+      <c r="P39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Q39" s="2"/>
+      <c r="R39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="S39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="T39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="U39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="V39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="W39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="X39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Y39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="Z39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AA39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AB39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AC39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AD39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AE39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AF39" t="s" s="2">
+        <v>191</v>
+      </c>
+      <c r="AG39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AH39" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI39" t="s" s="2">
+        <v>73</v>
+      </c>
+      <c r="AJ39" t="s" s="2">
         <v>73</v>
       </c>
     </row>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T08:31:26+00:00</t>
+    <t>2026-04-24T12:30:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
+++ b/ML-Entrees/ig/StructureDefinition-fr-lm-medication-prescription.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-24T12:30:57+00:00</t>
+    <t>2026-04-24T12:43:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
